--- a/stories/arbres/ATOM-TMP.SEM.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé s'assoit avec maman. Maman a un calendrier. Elle montre sept cases. Maman dit : il y a sept jours. Noé écoute. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au parc. Dimanche, on mange le gâteau. Maman dit : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Noé répète les sept jours dans l'ordre.</t>
+          <t>Noé s'assoit avec maman. Maman a un calendrier. Elle montre sept cases. Il y a sept jours. Noé écoute. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au parc. Dimanche, on mange le gâteau. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Noé répète les sept jours dans l'ordre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Noé s'assoit avec maman. Maman a un calendrier. Elle montre sept cases.
+maman|Il y a sept jours.
+narrateur|Noé écoute. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au parc. Dimanche, on mange le gâteau.
+maman|Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.
+narrateur|Noé répète les sept jours dans l'ordre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Après lundi, quel jour vient ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Noé pose un jeton sur lundi. Maman sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Noé répète les sept jours dans l'ordre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Après lundi, quel jour vient ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Noé a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1843,7 @@
           <t>narrateur|Noé pose un jeton sur lundi. Maman sourit.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.SEM.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Les sept jours de Noé</t>
+          <t>Les prunes de samedi</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir veut des prunes. Maman dit : demain, c'est samedi, le marché. Ils y vont trop tôt, c'est vendredi, volets fermés. Ils reviennent le bon jour. Les prunes sont là.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé s'assoit avec maman. Maman a un calendrier. Elle montre sept cases. Il y a sept jours. Noé écoute. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au parc. Dimanche, on mange le gâteau. Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Noé répète les sept jours dans l'ordre.</t>
+          <t>Le filet de maman sent encore le thym. Deux brins restent collés au filet. La cuisine est tiède, un peu sucrée. Une tache violette brille sur la table. C'est le jus d'une prune. Tu as vu la tache, Amir ? Elle est violette. C'est une prune d'hier. Je veux des prunes. Des prunes maintenant. Demain, c'est samedi. Samedi, c'est le marché. Le marché a des prunes. En ce moment, Amir prend le filet. Le filet est vide et mou. On y va ? On peut aller voir. Ils marchent dans la rue calme. Le pain froid sent encore. Un chat dort sur une marche. La boutique a les volets gris. C'est fermé. C'est encore vendredi. Vendredi, le marché dort. Amir se penche sous un volet. Il voit une caisse vide. Une mouche tourne, puis part. Toc toc. Personne ne répond. Les prunes ? Demain, les volets s'ouvrent. Demain, c'est samedi. La semaine a sept jours. On revient le bon jour. Je veux entrer. On rentre à la maison. Quel jour vient après vendredi ? Samedi. Oui. Ils reprennent le chemin. Les chaussures font un bruit doux. Le filet reste vide. La tache violette attend à la maison.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé s'assoit avec maman. Maman a un calendrier. Elle montre &lt;emphasis level="moderate"&gt;sept&lt;/emphasis&gt; cases. Maman dit : il y a sept jours. Noé écoute. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au parc. Dimanche, on mange le gâteau. Maman dit : lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche. Noé répète les sept jours dans l'ordre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le filet de maman sent encore le thym. Deux brins restent collés au filet. La cuisine est tiède, un peu sucrée. Une tache violette brille sur la table. C'est le jus d'une prune. Tu as vu la tache, Amir ? Elle est violette. C'est une prune d'hier. Je veux des prunes. Des prunes maintenant. Demain, c'est samedi. Samedi, c'est le marché. Le marché a des prunes. En ce moment, Amir prend le filet. Le filet est vide et mou. On y va ? On peut aller voir. Ils marchent dans la rue calme. Le pain froid sent encore. Un chat dort sur une marche. La boutique a les volets gris. C'est fermé. C'est encore vendredi. Vendredi, le marché dort. Amir se penche sous un volet. Il voit une caisse vide. Une mouche tourne, puis part. Toc toc. Personne ne répond. Les prunes ? Demain, les volets s'ouvrent. Demain, c'est samedi. La semaine a sept jours. On revient le bon jour. Je veux entrer. On rentre à la maison. Quel jour vient après vendredi ? Samedi. Oui. Ils reprennent le chemin. Les chaussures font un bruit doux. Le filet reste vide. La tache violette attend à la maison.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,11 +1324,49 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Noé s'assoit avec maman. Maman a un calendrier. Elle montre sept cases.
-maman|Il y a sept jours.
-narrateur|Noé écoute. Lundi, on met les chaussures. Mardi, on prend le cartable. Mercredi, on reste un peu à la maison. Jeudi, on revoit les copains. Vendredi, on chante à l'école. Samedi, on va au parc. Dimanche, on mange le gâteau.
-maman|Lundi, mardi, mercredi, jeudi, vendredi, samedi, dimanche.
-narrateur|Noé répète les sept jours dans l'ordre.</t>
+          <t>narrateur|Le filet de maman sent encore le thym.
+narrateur|Deux brins restent collés au filet.
+narrateur|La cuisine est tiède, un peu sucrée.
+narrateur|Une tache violette brille sur la table.
+narrateur|C'est le jus d'une prune.
+maman|Tu as vu la tache, Amir ?
+enfant-m|Elle est violette.
+maman|C'est une prune d'hier.
+enfant-m|Je veux des prunes.
+enfant-m|Des prunes maintenant.
+maman|Demain, c'est samedi.
+maman|Samedi, c'est le marché.
+maman|Le marché a des prunes.
+narrateur|En ce moment, Amir prend le filet.
+narrateur|Le filet est vide et mou.
+enfant-m|On y va ?
+maman|On peut aller voir.
+narrateur|Ils marchent dans la rue calme.
+narrateur|Le pain froid sent encore.
+narrateur|Un chat dort sur une marche.
+narrateur|La boutique a les volets gris.
+enfant-m|C'est fermé.
+maman|C'est encore vendredi.
+maman|Vendredi, le marché dort.
+narrateur|Amir se penche sous un volet.
+narrateur|Il voit une caisse vide.
+narrateur|Une mouche tourne, puis part.
+enfant-m|Toc toc.
+narrateur|Personne ne répond.
+enfant-m|Les prunes ?
+maman|Demain, les volets s'ouvrent.
+maman|Demain, c'est samedi.
+maman|La semaine a sept jours.
+maman|On revient le bon jour.
+enfant-m|Je veux entrer.
+maman|On rentre à la maison.
+maman|Quel jour vient après vendredi ?
+enfant-m|Samedi.
+maman|Oui.
+narrateur|Ils reprennent le chemin.
+narrateur|Les chaussures font un bruit doux.
+narrateur|Le filet reste vide.
+narrateur|La tache violette attend à la maison.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1348,12 +1398,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Après lundi, quel jour vient ?</t>
+          <t>Après vendredi, quel jour vient ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Après lundi, quel jour vient ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après vendredi, quel jour vient ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1363,12 +1413,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>mardi</t>
+          <t>samedi</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>mardi | c'est mardi | le mardi</t>
+          <t>samedi | le samedi | c'est samedi</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1383,7 +1433,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Lundi, puis mardi. Quel jour après lundi ?</t>
+          <t>Vendredi, c'est fermé. Quel jour vient après ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1432,7 +1482,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,10 +1554,9 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Après lundi, quel jour vient ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Après vendredi, quel jour vient ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,12 +1581,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine.</t>
+          <t>Le lendemain, la rue sent le fruit. Les volets sont ouverts, tout grands. C'est samedi, Amir. C'est le bon jour. Les prunes ! Des prunes violettes brillent en tas. Elles sont froides, un peu poudreuses. Amir tend le filet. Tu choisis ? Celles-là. Maman les glisse dans le filet. Le filet devient lourd, tout rond. Elles sont à nous. Merci, Amir. Tu as attendu samedi. Une prune roule vers le bord. Amir la rattrape avec la main. Elle est lisse et froide. On rentre ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé a dit les &lt;emphasis level="moderate"&gt;sept&lt;/emphasis&gt; jours dans l'ordre. Lundi commence. Dimanche termine.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le lendemain, la rue sent le fruit. Les volets sont ouverts, tout grands. C'est samedi, Amir. C'est le bon jour. Les prunes ! Des prunes violettes brillent en tas. Elles sont froides, un peu poudreuses. Amir tend le filet. Tu choisis ? Celles-là. Maman les glisse dans le filet. Le filet devient lourd, tout rond. Elles sont à nous. Merci, Amir. Tu as attendu samedi. Une prune roule vers le bord. Amir la rattrape avec la main. Elle est lisse et froide. On rentre ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1593,14 +1642,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1676,10 +1725,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noé a dit les sept jours dans l'ordre. Lundi commence. Dimanche termine.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le lendemain, la rue sent le fruit.
+narrateur|Les volets sont ouverts, tout grands.
+maman|C'est samedi, Amir.
+maman|C'est le bon jour.
+enfant-m|Les prunes !
+narrateur|Des prunes violettes brillent en tas.
+narrateur|Elles sont froides, un peu poudreuses.
+narrateur|Amir tend le filet.
+maman|Tu choisis ?
+enfant-m|Celles-là.
+narrateur|Maman les glisse dans le filet.
+narrateur|Le filet devient lourd, tout rond.
+enfant-m|Elles sont à nous.
+maman|Merci, Amir.
+maman|Tu as attendu samedi.
+narrateur|Une prune roule vers le bord.
+narrateur|Amir la rattrape avec la main.
+narrateur|Elle est lisse et froide.
+maman|On rentre ?
+enfant-m|Oui, maman.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,12 +1771,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Noé pose un jeton sur lundi. Maman sourit.</t>
+          <t>La table a encore la tache. Amir pose le filet dessus. Tu mords la tienne ? Oui. Le jus coule sur son menton. Il est froid, très sucré. Elle est bonne. Vendredi, c'était fermé. Samedi, le marché ouvre. J'ai attendu. Oui. Le thym sent encore le filet. Deux noyaux brillent dans une coupelle. On en garde pour demain ? Demain, c'est dimanche. Oui. Amir essuie son menton. La tache violette a un ami.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé pose un jeton sur lundi. Maman sourit.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La table a encore la tache. Amir pose le filet dessus. Tu mords la tienne ? Oui. Le jus coule sur son menton. Il est froid, très sucré. Elle est bonne. Vendredi, c'était fermé. Samedi, le marché ouvre. J'ai attendu. Oui. Le thym sent encore le filet. Deux noyaux brillent dans une coupelle. On en garde pour demain ? Demain, c'est dimanche. Oui. Amir essuie son menton. La tache violette a un ami.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1765,14 +1832,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1840,10 +1907,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Noé pose un jeton sur lundi. Maman sourit.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|La table a encore la tache.
+narrateur|Amir pose le filet dessus.
+maman|Tu mords la tienne ?
+enfant-m|Oui.
+narrateur|Le jus coule sur son menton.
+narrateur|Il est froid, très sucré.
+enfant-m|Elle est bonne.
+maman|Vendredi, c'était fermé.
+maman|Samedi, le marché ouvre.
+enfant-m|J'ai attendu.
+maman|Oui.
+narrateur|Le thym sent encore le filet.
+narrateur|Deux noyaux brillent dans une coupelle.
+maman|On en garde pour demain ?
+enfant-m|Demain, c'est dimanche.
+maman|Oui.
+narrateur|Amir essuie son menton.
+narrateur|La tache violette a un ami.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Les doigts d'Amir sont un peu violets. J'ai mes prunes. Oui. Le bon jour était samedi. Le filet sent le thym et le fruit.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les doigts d'Amir sont un peu violets. J'ai mes prunes. Oui. Le bon jour était samedi. Le filet sent le thym et le fruit.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1929,14 +2012,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2008,10 +2091,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Les doigts d'Amir sont un peu violets.
+enfant-m|J'ai mes prunes.
+maman|Oui.
+maman|Le bon jour était samedi.
+narrateur|Le filet sent le thym et le fruit.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2030,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2154,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.SEM.001-01.xlsx
+++ b/stories/arbres/ATOM-TMP.SEM.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison</t>
+          <t>cuisine, puis rue de la boutique</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Noé, maman</t>
+          <t>Amir, maman</t>
         </is>
       </c>
     </row>
